--- a/templates/Import customs entries template.xlsx
+++ b/templates/Import customs entries template.xlsx
@@ -397,18 +397,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:V1"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="14.83203125" customWidth="1"/>
     <col min="4" max="4" width="14.83203125" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="22.83203125" customWidth="1"/>
-    <col min="7" max="7" width="23.83203125" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
     <col min="8" max="8" width="14.83203125" customWidth="1"/>
     <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="15.83203125" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="22.83203125" customWidth="1"/>
+    <col min="12" max="12" width="23.83203125" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" customWidth="1"/>
+    <col min="14" max="14" width="14.83203125" customWidth="1"/>
+    <col min="15" max="15" width="14.83203125" customWidth="1"/>
+    <col min="16" max="16" width="14.83203125" customWidth="1"/>
+    <col min="17" max="17" width="15.83203125" customWidth="1"/>
+    <col min="18" max="18" width="14.83203125" customWidth="1"/>
+    <col min="19" max="19" width="14.83203125" customWidth="1"/>
+    <col min="20" max="20" width="14.83203125" customWidth="1"/>
+    <col min="21" max="21" width="14.83203125" customWidth="1"/>
+    <col min="22" max="22" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -422,30 +434,66 @@
         <v>Invoice No</v>
       </c>
       <c r="D1" t="str">
+        <v>Item No</v>
+      </c>
+      <c r="E1" t="str">
+        <v>HS Code</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="G1" t="str">
+        <v>UOM</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Quantity</v>
+      </c>
+      <c r="I1" t="str">
         <v>Currency</v>
       </c>
-      <c r="E1" t="str">
+      <c r="J1" t="str">
         <v>Ex. Rate</v>
       </c>
-      <c r="F1" t="str">
+      <c r="K1" t="str">
         <v>Invoice Value (FC)</v>
       </c>
-      <c r="G1" t="str">
+      <c r="L1" t="str">
         <v>Customs Value (LKR)</v>
       </c>
-      <c r="H1" t="str">
+      <c r="M1" t="str">
+        <v>CID Amount</v>
+      </c>
+      <c r="N1" t="str">
+        <v>CID Code</v>
+      </c>
+      <c r="O1" t="str">
+        <v>PAL Amount</v>
+      </c>
+      <c r="P1" t="str">
+        <v>PAL Code</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>SSCL Amount</v>
+      </c>
+      <c r="R1" t="str">
+        <v>SSCL Code</v>
+      </c>
+      <c r="S1" t="str">
+        <v>VAT Base</v>
+      </c>
+      <c r="T1" t="str">
         <v>VAT Amount</v>
       </c>
-      <c r="I1" t="str">
+      <c r="U1" t="str">
+        <v>VAT Code</v>
+      </c>
+      <c r="V1" t="str">
         <v>Supplier</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Description</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:V1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/templates/Import customs entries template.xlsx
+++ b/templates/Import customs entries template.xlsx
@@ -397,103 +397,107 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:W1"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="14.83203125" customWidth="1"/>
     <col min="4" max="4" width="14.83203125" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
     <col min="8" max="8" width="14.83203125" customWidth="1"/>
     <col min="9" max="9" width="14.83203125" customWidth="1"/>
     <col min="10" max="10" width="14.83203125" customWidth="1"/>
-    <col min="11" max="11" width="22.83203125" customWidth="1"/>
-    <col min="12" max="12" width="23.83203125" customWidth="1"/>
-    <col min="13" max="13" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="14.83203125" customWidth="1"/>
+    <col min="12" max="12" width="22.83203125" customWidth="1"/>
+    <col min="13" max="13" width="23.83203125" customWidth="1"/>
     <col min="14" max="14" width="14.83203125" customWidth="1"/>
     <col min="15" max="15" width="14.83203125" customWidth="1"/>
     <col min="16" max="16" width="14.83203125" customWidth="1"/>
-    <col min="17" max="17" width="15.83203125" customWidth="1"/>
-    <col min="18" max="18" width="14.83203125" customWidth="1"/>
+    <col min="17" max="17" width="14.83203125" customWidth="1"/>
+    <col min="18" max="18" width="15.83203125" customWidth="1"/>
     <col min="19" max="19" width="14.83203125" customWidth="1"/>
     <col min="20" max="20" width="14.83203125" customWidth="1"/>
     <col min="21" max="21" width="14.83203125" customWidth="1"/>
     <col min="22" max="22" width="14.83203125" customWidth="1"/>
+    <col min="23" max="23" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>File Name</v>
+      </c>
+      <c r="B1" t="str">
         <v>Cusdec No</v>
       </c>
-      <c r="B1" t="str">
+      <c r="C1" t="str">
         <v>Date</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>Invoice No</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>Item No</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>HS Code</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Description</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>UOM</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>Quantity</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>Currency</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>Ex. Rate</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>Invoice Value (FC)</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>Customs Value (LKR)</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>CID Amount</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>CID Code</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>PAL Amount</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>PAL Code</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>SSCL Amount</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>SSCL Code</v>
       </c>
-      <c r="S1" t="str">
+      <c r="T1" t="str">
         <v>VAT Base</v>
       </c>
-      <c r="T1" t="str">
+      <c r="U1" t="str">
         <v>VAT Amount</v>
       </c>
-      <c r="U1" t="str">
+      <c r="V1" t="str">
         <v>VAT Code</v>
       </c>
-      <c r="V1" t="str">
+      <c r="W1" t="str">
         <v>Supplier</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:V1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:W1"/>
   </ignoredErrors>
 </worksheet>
 </file>